--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260820.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260820.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>3.84%</t>
         </is>
       </c>
     </row>
@@ -638,68 +638,68 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.84%</t>
+          <t>3.79%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>6,066,000</t>
+          <t>21,637,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>21,610,000</t>
+          <t>6,066,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>4,173,166,066</t>
+          <t>47,925,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -711,39 +711,39 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>47,874,000</t>
+          <t>35,649,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>35,599,000</t>
+          <t>3,875,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>3,875,000</t>
+          <t>4,036,790,722</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
@@ -792,95 +792,95 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>11,265,000</t>
+          <t>20,426,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>20,426,000</t>
+          <t>11,265,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>202609WTX</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>115/09台股期貨</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>26,121,000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>202609WTX</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>115/09台股期貨</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>26,162,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>34,668,000</t>
+          <t>34,731,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -968,68 +968,68 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>22,764,000</t>
+          <t>36,304,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>36,256,000</t>
+          <t>4,161,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2,187,000</t>
+          <t>22,764,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,22 +1041,22 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>4,161,000</t>
+          <t>2,187,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -1139,122 +1139,122 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>4,234,000</t>
+          <t>4,761,400</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>18,002,000</t>
+          <t>15,213,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>41,037,000</t>
+          <t>18,002,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>15,188,000</t>
+          <t>41,037,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,526,561,747</t>
+          <t>14,264,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>14,241,000</t>
+          <t>2,558,801,747</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -1271,78 +1271,78 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>6,077,000</t>
+          <t>6,179,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,600,000</t>
+          <t>4,984,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,984,000</t>
+          <t>9,652,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>9,652,000</t>
+          <t>6,600,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1359,100 +1359,100 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>14,372,000</t>
+          <t>14,405,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>3,901,000</t>
+          <t>24,954,004</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>24,122,004</t>
+          <t>15,340,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>7,883,000</t>
+          <t>3,901,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>14,037,000</t>
+          <t>7,883,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>23,651,000</t>
+          <t>23,694,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -1540,73 +1540,73 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>8,918,000</t>
+          <t>2,298,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2,298,000</t>
+          <t>8,918,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,586,000</t>
+          <t>52,656,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1623,78 +1623,78 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>47,991,000</t>
+          <t>48,160,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>18,852,000</t>
+          <t>1,586,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>50,097,000</t>
+          <t>6,733,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>6,467,000</t>
+          <t>18,852,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>18,334,000</t>
+          <t>18,415,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>17,362,000</t>
+          <t>18,144,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-58,544,545</t>
+          <t>-35,488,368</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
     </row>
